--- a/out/MLP-S4_repeat_4_000001.xlsx
+++ b/out/MLP-S4_repeat_4_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>3.60677127013091</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>3.60677127013091</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>3.60677127013091</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.2927231521932763</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>3.60677127013091</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.2927231521932763</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.2927231521932763</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>3.60677127013091</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.60677127013091</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>3.60677127013091</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.60677127013091</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0003945843033447163</v>
+        <v>-0.0002577772592762485</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1698964376188103</v>
+        <v>0.1109912964866739</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.60677127013091</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.3402464988813396</v>
+        <v>0.2222790143693965</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.6563997888065459</v>
+        <v>0.4288180764371204</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.60677127013091</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.483585550332536</v>
+        <v>0.9692091466867835</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.2019127636366966</v>
+        <v>0.1319073531543832</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>3.60677127013091</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.230178685208101</v>
+        <v>0.8036612722103675</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.04096960170000215</v>
+        <v>0.02676498316748519</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>3.60677127013091</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.109889251721868</v>
+        <v>0.7250775289252778</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.03548113809140905</v>
+        <v>0.02317966493616919</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.139837350246333</v>
+        <v>0.7446422865812115</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01734592315607381</v>
+        <v>0.01133166228766422</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.13900227506361</v>
+        <v>0.7440967471048301</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.008277655291284852</v>
+        <v>0.005405853706746107</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.138189407272213</v>
+        <v>0.7435639760162698</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.003445489838446076</v>
+        <v>0.002249119612111675</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.13679311085537</v>
+        <v>0.7426500378087603</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002386409947590952</v>
+        <v>0.001557634767302897</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.138117531887927</v>
+        <v>0.743513589525875</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0009936448866797775</v>
+        <v>0.0006470184679483451</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>3.00677127013091</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.137715039579769</v>
+        <v>0.7432489379781341</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0005128329986080802</v>
+        <v>0.0003330948352202433</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>3.60677127013091</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.137746019918212</v>
+        <v>0.7432674535704525</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.00019812240145624</v>
+        <v>0.0001277906138719088</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.137629347857216</v>
+        <v>0.7431893986409644</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0001060908526991624</v>
+        <v>6.772442418965789e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.13764265517039</v>
+        <v>0.7431963833253616</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.977315802226313e-05</v>
+        <v>3.057431912786162e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.137635985008534</v>
+        <v>0.7431902906099691</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>2.05756295486964e-05</v>
+        <v>1.205041969913093e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.137627832813646</v>
+        <v>0.7431832104029619</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>6.068124478464586e-06</v>
+        <v>2.378749652309724e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.137619289921977</v>
+        <v>0.7431758963017496</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-3.91678593955831e-08</v>
+        <v>-1.69277857293039e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.137613081127005</v>
+        <v>0.7431701223228127</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.09281402832566e-06</v>
+        <v>-3.728542685550439e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.13760683175957</v>
+        <v>0.7431643531799451</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.452445000690905e-06</v>
+        <v>-4.634963333793937e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.137600880748811</v>
+        <v>0.7431588095118427</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.555348042317843e-06</v>
+        <v>-4.777674021158921e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.137596038441368</v>
+        <v>0.7431538883581212</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.13759111723982</v>
+        <v>0.7431539282135935</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.137591109268725</v>
+        <v>0.743153920242499</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.137591268690614</v>
+        <v>0.7431540796643882</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>3.60677127013091</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.137591173037481</v>
+        <v>0.7431539840112548</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.137591523765638</v>
+        <v>0.7431543347394111</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.137591276661709</v>
+        <v>0.7431540876354826</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.137591236806237</v>
+        <v>0.7431540477800104</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.137591173037481</v>
+        <v>0.7431539840112548</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.137591244777331</v>
+        <v>0.7431540557511048</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.137591173037481</v>
+        <v>0.7431539840112548</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>3.60677127013091</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.137591276661709</v>
+        <v>0.7431540876354826</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.137591372314842</v>
+        <v>0.7431541832886164</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.137591308546087</v>
+        <v>0.7431541195198604</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.137591268690614</v>
+        <v>0.7431540796643882</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.137591244777331</v>
+        <v>0.7431540557511048</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.137590997673403</v>
+        <v>0.7431538086471767</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.137590917962458</v>
+        <v>0.7431537289362319</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.137590965789025</v>
+        <v>0.7431537767627987</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.137591085355442</v>
+        <v>0.7431538963292157</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.137591069413253</v>
+        <v>0.7431538803870268</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.137591085355442</v>
+        <v>0.7431538963292157</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.137591069413253</v>
+        <v>0.7431538803870268</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.137591125210914</v>
+        <v>0.7431539361846881</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.137591125210914</v>
+        <v>0.7431539361846881</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>3.60677127013091</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.137591125210914</v>
+        <v>0.7431539361846881</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.137591276661709</v>
+        <v>0.7431540876354826</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>3.60677127013091</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.137591491881259</v>
+        <v>0.7431543028550331</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.13759140419922</v>
+        <v>0.7431542151729942</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.2927231521932763</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.137591356372653</v>
+        <v>0.7431541673464275</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.13759140419922</v>
+        <v>0.7431542151729942</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.137591220864048</v>
+        <v>0.7431540318378215</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.137591228835142</v>
+        <v>0.7431540398089159</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.137591236806237</v>
+        <v>0.7431540477800104</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.137591244777331</v>
+        <v>0.7431540557511048</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.137591244777331</v>
+        <v>0.7431540557511048</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.137591284632803</v>
+        <v>0.7431540956065771</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.137591348401559</v>
+        <v>0.743154159375333</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.137591459996881</v>
+        <v>0.7431542709706553</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.137591507823448</v>
+        <v>0.7431543187972222</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.137591467967976</v>
+        <v>0.7431542789417498</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.137591396228126</v>
+        <v>0.7431542072018997</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.137591515794543</v>
+        <v>0.7431543267683166</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.137591356372653</v>
+        <v>0.7431541673464275</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.137591125210914</v>
+        <v>0.7431539361846881</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.137591077384348</v>
+        <v>0.7431538883581212</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.137591109268725</v>
+        <v>0.743153920242499</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.137591173037481</v>
+        <v>0.7431539840112548</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.137591173037481</v>
+        <v>0.7431539840112548</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.137591093326537</v>
+        <v>0.7431539043003101</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.13759097376012</v>
+        <v>0.7431537847338932</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.137590933904647</v>
+        <v>0.7431537448784208</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.137591077384348</v>
+        <v>0.7431538883581212</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.137591212892953</v>
+        <v>0.743154023866727</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.137591196950764</v>
+        <v>0.7431540079245381</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.137591173037481</v>
+        <v>0.7431539840112548</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.137591133182009</v>
+        <v>0.7431539441557825</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.137591029557781</v>
+        <v>0.7431538405315545</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.137590909991364</v>
+        <v>0.7431537209651374</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.137591029557781</v>
+        <v>0.7431538405315545</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.137591077384348</v>
+        <v>0.7431538883581212</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.137591173037481</v>
+        <v>0.7431539840112548</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.137591053471064</v>
+        <v>0.7431538644448379</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.8927231521932764</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.137591061442159</v>
+        <v>0.7431538724159323</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_4_000001.xlsx
+++ b/out/MLP-S4_repeat_4_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.8927231521932764</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>3.60677127013091</v>
+        <v>1.536187288701382</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>3.60677127013091</v>
+        <v>2.427500299518339</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>3.60677127013091</v>
+        <v>1.536187288701382</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.2927231521932763</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.2464387329325323</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.8927231521932764</v>
+        <v>0.4448742778844246</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>3.60677127013091</v>
+        <v>0.4448742778844246</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.2927231521932763</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.2464387329325323</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.2464387329325323</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.8927231521932764</v>
+        <v>0.4448742778844246</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>3.60677127013091</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.2927231521932763</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.2464387329325323</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.8927231521932764</v>
+        <v>0.4448742778844246</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>3.60677127013091</v>
+        <v>1.536187288701382</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.60677127013091</v>
+        <v>2.427500299518339</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>3.60677127013091</v>
+        <v>2.427500299518339</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.60677127013091</v>
+        <v>2.427500299518339</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0003945843033447163</v>
+        <v>-0.0002982669498466421</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1698964376188103</v>
+        <v>0.128425088747479</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.60677127013091</v>
+        <v>2.427500299518339</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.3402464988813396</v>
+        <v>0.2571929101023385</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.6563997888065459</v>
+        <v>0.4961732084811908</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.60677127013091</v>
+        <v>2.427500299518339</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.483585550332536</v>
+        <v>1.121444310520404</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.2019127636366966</v>
+        <v>0.1526261693445941</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>3.60677127013091</v>
+        <v>2.427500299518339</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.230178685208101</v>
+        <v>0.9298936704669809</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.04096960170000215</v>
+        <v>0.03096898509247407</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>3.60677127013091</v>
+        <v>1.536187288701381</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.109889251721868</v>
+        <v>0.8389667022309901</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.03548113809140905</v>
+        <v>0.02682051744119278</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.8927231521932764</v>
+        <v>0.4448742778844246</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.139837350246333</v>
+        <v>0.8616045153913041</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01734592315607381</v>
+        <v>0.01311159244695156</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.13900227506361</v>
+        <v>0.8609732873578106</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.008277655291284852</v>
+        <v>0.006255767996074466</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.138189407272213</v>
+        <v>0.8603576212003792</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.003445489838446076</v>
+        <v>0.002603187301245541</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.13679311085537</v>
+        <v>0.8593009283064406</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002386409947590952</v>
+        <v>0.001803026301131204</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.8927231521932764</v>
+        <v>0.4448742778844246</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.138117531887927</v>
+        <v>0.8603008748117243</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0009936448866797775</v>
+        <v>0.0007494601047109804</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>3.00677127013091</v>
+        <v>1.336187288701382</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.137715039579769</v>
+        <v>0.8599954482465659</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0005128329986080802</v>
+        <v>0.0003865485641088193</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>3.60677127013091</v>
+        <v>1.536187288701381</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.137746019918212</v>
+        <v>0.8600176540250531</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.00019812240145624</v>
+        <v>0.0001487851773299181</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.2927231521932763</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.137629347857216</v>
+        <v>0.8599282150733228</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0001060908526991624</v>
+        <v>7.860445615503979e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.2464387329325323</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.13764265517039</v>
+        <v>0.8599370405685667</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.977315802226313e-05</v>
+        <v>3.622103644974442e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.137635985008534</v>
+        <v>0.8599307756715394</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>2.05756295486964e-05</v>
+        <v>1.471454777712014e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.137627832813646</v>
+        <v>0.8599233704321874</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>6.068124478464586e-06</v>
+        <v>3.301093358848441e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.137619289921977</v>
+        <v>0.8599156953284733</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-3.91678593955831e-08</v>
+        <v>-1.279375894546688e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.137613081127005</v>
+        <v>0.8599097767756024</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.09281402832566e-06</v>
+        <v>-3.410678356938051e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.13760683175957</v>
+        <v>0.859903815347018</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.452445000690905e-06</v>
+        <v>-4.634963333793937e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.137600880748811</v>
+        <v>0.8598981361703097</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.555348042317843e-06</v>
+        <v>-4.777674021158921e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.137596038441368</v>
+        <v>0.8598932548720604</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.13759111723982</v>
+        <v>0.8598883336705125</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.137591109268725</v>
+        <v>0.8598883256994181</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.8927231521932764</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.137591268690614</v>
+        <v>0.8598884851213072</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>3.60677127013091</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.137591173037481</v>
+        <v>0.8598883894681737</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.2927231521932763</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.137591523765638</v>
+        <v>0.85988874019633</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.2464387329325323</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.137591276661709</v>
+        <v>0.8598884930924017</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.2464387329325323</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.137591236806237</v>
+        <v>0.8598884532369294</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.137591173037481</v>
+        <v>0.8598883894681737</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.137591244777331</v>
+        <v>0.8598884612080239</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8927231521932764</v>
+        <v>0.4448742778844246</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.137591173037481</v>
+        <v>0.8598883894681737</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>3.60677127013091</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.137591276661709</v>
+        <v>0.8598884930924017</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.2927231521932763</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.137591372314842</v>
+        <v>0.8598885887455353</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.2464387329325323</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.137591308546087</v>
+        <v>0.8598885249767795</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.137591268690614</v>
+        <v>0.8598884851213072</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.137591244777331</v>
+        <v>0.8598884612080239</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.137590997673403</v>
+        <v>0.8598882141040957</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.137590917962458</v>
+        <v>0.8598881343931509</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.137590965789025</v>
+        <v>0.8598881822197176</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.137591085355442</v>
+        <v>0.8598883017861347</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.137591069413253</v>
+        <v>0.8598882858439458</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.137591085355442</v>
+        <v>0.8598883017861347</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.137591069413253</v>
+        <v>0.8598882858439458</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.137591125210914</v>
+        <v>0.859888341641607</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.8927231521932764</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.137591125210914</v>
+        <v>0.859888341641607</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>3.60677127013091</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.137591125210914</v>
+        <v>0.859888341641607</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.2927231521932763</v>
+        <v>1.536187288701382</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.137591276661709</v>
+        <v>0.8598884930924017</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>3.60677127013091</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.137591491881259</v>
+        <v>0.8598887083119522</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.2927231521932763</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.13759140419922</v>
+        <v>0.8598886206299132</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.2927231521932763</v>
+        <v>-0.2464387329325323</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.137591356372653</v>
+        <v>0.8598885728033464</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.13759140419922</v>
+        <v>0.8598886206299132</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.137591220864048</v>
+        <v>0.8598884372947405</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.137591228835142</v>
+        <v>0.859888445265835</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.137591236806237</v>
+        <v>0.8598884532369294</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.137591244777331</v>
+        <v>0.8598884612080239</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.137591244777331</v>
+        <v>0.8598884612080239</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.137591284632803</v>
+        <v>0.8598885010634961</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.137591348401559</v>
+        <v>0.859888564832252</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.137591459996881</v>
+        <v>0.8598886764275744</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.137591507823448</v>
+        <v>0.8598887242541411</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.137591467967976</v>
+        <v>0.8598886843986688</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.137591396228126</v>
+        <v>0.8598886126588187</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.137591515794543</v>
+        <v>0.8598887322252355</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.137591356372653</v>
+        <v>0.8598885728033464</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.137591125210914</v>
+        <v>0.859888341641607</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.137591077384348</v>
+        <v>0.8598882938150403</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.137591109268725</v>
+        <v>0.8598883256994181</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.137591173037481</v>
+        <v>0.8598883894681737</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.137591173037481</v>
+        <v>0.8598883894681737</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.137591093326537</v>
+        <v>0.8598883097572292</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.13759097376012</v>
+        <v>0.8598881901908121</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.137590933904647</v>
+        <v>0.8598881503353398</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.137591077384348</v>
+        <v>0.8598882938150403</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.137591212892953</v>
+        <v>0.859888429323646</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.137591196950764</v>
+        <v>0.8598884133814571</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.137591173037481</v>
+        <v>0.8598883894681737</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.137591133182009</v>
+        <v>0.8598883496127014</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.137591029557781</v>
+        <v>0.8598882459884736</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.137590909991364</v>
+        <v>0.8598881264220565</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.137591029557781</v>
+        <v>0.8598882459884736</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.137591077384348</v>
+        <v>0.8598882938150403</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.137591173037481</v>
+        <v>0.8598883894681737</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.137591053471064</v>
+        <v>0.8598882699017569</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.137591061442159</v>
+        <v>0.8598882778728514</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_4_000001.xlsx
+++ b/out/MLP-S4_repeat_4_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.3543838858604431</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4639541208744049</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.58</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.3863641917705536</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.3556992709636688</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.3936363458633423</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4845869839191437</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.3550336956977844</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.3604236245155334</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.412377655506134</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.3421077132225037</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.3882408142089844</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.3660984337329865</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4304804801940918</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.6448742778844246</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.5261687040328979</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.536187288701382</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.5694541335105896</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.427500299518339</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.5715757608413696</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.536187288701382</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.456194669008255</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.6448742778844246</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4784612655639648</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.2464387329325323</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4822880625724792</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.413055956363678</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.4094627201557159</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.4497503638267517</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.3</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.4936332404613495</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.4448742778844246</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.5293112993240356</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.4448742778844246</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.454956591129303</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.6448742778844246</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.4472838044166565</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.2464387329325323</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.4371819198131561</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.2464387329325323</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.3890890181064606</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4464235901832581</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.4448742778844246</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.5648875832557678</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.6448742778844246</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4074866473674774</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.6448742778844246</v>
+        <v>-0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.4610025584697723</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.2464387329325323</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.3942969739437103</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.3803363144397736</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.3789612650871277</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.4242592453956604</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.4351861476898193</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.4570079743862152</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.4448742778844246</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.6009241342544556</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.536187288701382</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.6482706665992737</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.427500299518339</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.7622419595718384</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.427500299518339</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.8064717650413513</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.427500299518339</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002982669498466421</v>
+        <v>-0.0001816752822221024</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.128425088747479</v>
+        <v>0.07822410178061202</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.9066095352172852</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.427500299518339</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2571929101023385</v>
+        <v>0.1566569630070983</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4961732084811908</v>
+        <v>0.3022210742498265</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.9008415937423706</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.427500299518339</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.121444310520404</v>
+        <v>0.6830750487817598</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1526261693445941</v>
+        <v>0.09296489660347235</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.6666324138641357</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.427500299518339</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.9298936704669809</v>
+        <v>0.5664011813620098</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.03096898509247407</v>
+        <v>0.01886306248949166</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.5847555994987488</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.536187288701381</v>
+        <v>-0.3</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.8389667022309901</v>
+        <v>0.5110173888417329</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02682051744119278</v>
+        <v>0.01633660823303623</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.3572762608528137</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.4448742778844246</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.8616045153913041</v>
+        <v>0.5248062758631562</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01311159244695156</v>
+        <v>0.007985702361668543</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.4428823590278625</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.8609732873578106</v>
+        <v>0.524420894243811</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.006255767996074466</v>
+        <v>0.003808255384588791</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.4024608135223389</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.8603576212003792</v>
+        <v>0.5240439424238605</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002603187301245541</v>
+        <v>0.001583850919478074</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.4171430468559265</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.8593009283064406</v>
+        <v>0.5233983419913631</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001803026301131204</v>
+        <v>0.001096175216267276</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.380896121263504</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.4448742778844246</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.8603008748117243</v>
+        <v>0.5240054028804111</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0007494601047109804</v>
+        <v>0.0004543766478726977</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.5204257369041443</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.336187288701382</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.8599954482465659</v>
+        <v>0.5238174288811471</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003865485641088193</v>
+        <v>0.0002335372651652704</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.5321497321128845</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.536187288701381</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.8600176540250531</v>
+        <v>0.5238290030499527</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001487851773299181</v>
+        <v>8.842580738814138e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.3680123090744019</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.6448742778844246</v>
+        <v>0.16</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.8599282150733228</v>
+        <v>0.5237725621866074</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>7.860445615503979e-05</v>
+        <v>4.596436025889411e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.3693356812000275</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.2464387329325323</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.8599370405685667</v>
+        <v>0.5237760087290115</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.622103644974442e-05</v>
+        <v>2.041022794847258e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.2830962538719177</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.8599307756715394</v>
+        <v>0.5237702339116556</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.471454777712014e-05</v>
+        <v>6.722163543152517e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.3109744787216187</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.8599233704321874</v>
+        <v>0.5237637718849604</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.301093358848441e-06</v>
+        <v>7.289038596293463e-08</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>0.3153224289417267</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.8599156953284733</v>
+        <v>0.5237571092005268</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.279375894546688e-06</v>
+        <v>-2.519583929697793e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.3375851511955261</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8599097767756024</v>
+        <v>0.5237515287163241</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.410678356938051e-06</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.3550535142421722</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.859903815347018</v>
+        <v>0.5237459518591734</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.3434946537017822</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.8598981361703097</v>
+        <v>0.5237405445165164</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.39540034532547</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.8598932548720604</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.3260156512260437</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.8598883336705125</v>
+        <v>0.5237356632182673</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>0.4323358833789825</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.8598883256994181</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.3679771423339844</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.6448742778844246</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.8598884851213072</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.5054531693458557</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.6448742778844246</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.8598883894681737</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.4224104285240173</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.6448742778844246</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.85988874019633</v>
+        <v>0.5237360697440847</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.3383293449878693</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.2464387329325323</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.8598884930924017</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.3689468801021576</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.2464387329325323</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.8598884532369294</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.2859067916870117</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.8598883894681737</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.2794269919395447</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.8598884612080239</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.2900468707084656</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.4448742778844246</v>
+        <v>0.16</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.8598883894681737</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.6988640427589417</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.6448742778844246</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.8598884930924017</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.4408175349235535</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.6448742778844246</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.8598885887455353</v>
+        <v>0.52373591829329</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.2981027066707611</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.2464387329325323</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.8598885249767795</v>
+        <v>0.5237358545245342</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.2550733387470245</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.16</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.8598884851213072</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.3959951996803284</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.8598884612080239</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.3491063117980957</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.8598882141040957</v>
+        <v>0.5237355436518504</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.3189118802547455</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.8598881343931509</v>
+        <v>0.5237354639409056</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.3508398830890656</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.8598881822197176</v>
+        <v>0.5237355117674724</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.3309365808963776</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.8598883017861347</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.4062139391899109</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.8598882858439458</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.3807981312274933</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.8598883017861347</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.4121608734130859</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.8598882858439458</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.3851372301578522</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.859888341641607</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3302314877510071</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.6448742778844246</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.859888341641607</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.5088514685630798</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.6448742778844246</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.859888341641607</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.380011647939682</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.536187288701382</v>
+        <v>0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.8598884930924017</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.5372994542121887</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.6448742778844246</v>
+        <v>-0.3</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.8598887083119522</v>
+        <v>0.5237360378597069</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.3282062113285065</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.6448742778844246</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.8598886206299132</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.3519173860549927</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.2464387329325323</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.8598885728033464</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.3778466284275055</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.8598886206299132</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.2961806654930115</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.8598884372947405</v>
+        <v>0.5237357668424952</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.2809939682483673</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.859888445265835</v>
+        <v>0.5237357748135897</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.3733959197998047</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.8598884532369294</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.3185776770114899</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.8598884612080239</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.3079713582992554</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.3</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.8598884612080239</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.4636566638946533</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.8598885010634961</v>
+        <v>0.5237358306112508</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.41880202293396</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.859888564832252</v>
+        <v>0.5237358943800067</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.4260884523391724</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.8598886764275744</v>
+        <v>0.5237360059753291</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.3152928948402405</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.8598887242541411</v>
+        <v>0.5237360538018958</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.3837118744850159</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.8598886843986688</v>
+        <v>0.5237360139464236</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.4150679409503937</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.8598886126588187</v>
+        <v>0.5237359422065735</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.4473417401313782</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.8598887322252355</v>
+        <v>0.5237360617729903</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.4615462124347687</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.8598885728033464</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.3567808270454407</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.3</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.859888341641607</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.3818993866443634</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.8598882938150403</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.3092853724956512</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.8598883256994181</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.3677166402339935</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.8598883894681737</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.3221032917499542</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.8598883894681737</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.3502029478549957</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.8598883097572292</v>
+        <v>0.5237356393049839</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.382222980260849</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.8598881901908121</v>
+        <v>0.5237355197385668</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>0.3795664310455322</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.8598881503353398</v>
+        <v>0.5237354798830945</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.4136258363723755</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.8598882938150403</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.3848286867141724</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.3</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.859888429323646</v>
+        <v>0.5237357588714008</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.3269741237163544</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.16</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.8598884133814571</v>
+        <v>0.5237357429292118</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.3454080820083618</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.8598883894681737</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.3562626242637634</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.8598883496127014</v>
+        <v>0.5237356791604562</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.4076589345932007</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.8598882459884736</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.4577839076519012</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.3</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.8598881264220565</v>
+        <v>0.5237354559698112</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.3432962894439697</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.8598882459884736</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.3854700326919556</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.8598882938150403</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.3074657917022705</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.8598883894681737</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.3437304496765137</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.8598882699017569</v>
+        <v>0.5237355994495116</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4371046423912048</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.8598882778728514</v>
+        <v>0.5237356074206061</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_4_000001.xlsx
+++ b/out/MLP-S4_repeat_4_000001.xlsx
@@ -41489,7 +41489,7 @@
         <v>0.4171430468559265</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC51" t="n">
         <v>0.5233983419913631</v>
@@ -42284,7 +42284,7 @@
         <v>0.380896121263504</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC52" t="n">
         <v>0.5240054028804111</v>
@@ -43079,7 +43079,7 @@
         <v>0.5204257369041443</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC53" t="n">
         <v>0.5238174288811471</v>
@@ -43874,7 +43874,7 @@
         <v>0.5321497321128845</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.1600000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC54" t="n">
         <v>0.5238290030499527</v>
@@ -44669,7 +44669,7 @@
         <v>0.3680123090744019</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.16</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC55" t="n">
         <v>0.5237725621866074</v>
